--- a/source/sfp/1_water/sfp_101_nl_transecten_rivier/data/overzicht_vars.xlsx
+++ b/source/sfp/1_water/sfp_101_nl_transecten_rivier/data/overzicht_vars.xlsx
@@ -36,9 +36,6 @@
     <t>Methode</t>
   </si>
   <si>
-    <t>Stroomsnelheid</t>
-  </si>
-  <si>
     <t>Bodem</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
   </si>
   <si>
     <t>%</t>
-  </si>
-  <si>
-    <t>Substraatsamenstelling</t>
   </si>
   <si>
     <t>visueel</t>
@@ -160,6 +154,12 @@
   </si>
   <si>
     <t>fijn grind</t>
+  </si>
+  <si>
+    <t>Substraat- samenstelling</t>
+  </si>
+  <si>
+    <t>Stroom- snelheid</t>
   </si>
 </sst>
 </file>
@@ -246,24 +246,7 @@
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -568,272 +551,272 @@
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
